--- a/outputs/51354.xlsx
+++ b/outputs/51354.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">Data</t>
   </si>
@@ -40,16 +40,31 @@
     <t xml:space="preserve">Monthly ISEA Progress Report - Oct 21</t>
   </si>
   <si>
+    <t xml:space="preserve">Nov 21</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monthly ISEA Progress Report - Nov 21</t>
   </si>
   <si>
+    <t xml:space="preserve">Dec 21</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monthly ISEA Progress Report - Dec 21</t>
   </si>
   <si>
+    <t xml:space="preserve">Jan 22</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monthly ISEA Progress Report Jan 22</t>
   </si>
   <si>
+    <t xml:space="preserve">Feb 22</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monthly ISEA Progress Report - Feb 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mar 22</t>
   </si>
 </sst>
 </file>
@@ -159,48 +174,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -456,140 +475,130 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="40.5" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="e">
+      <c r="B2" s="6" t="e">
         <f aca="false">TEXT(DATE(RIGHT(A2,2),RIGHT(A2,6),),"MMM YY")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C2" s="5" t="str">
+      <c r="C2" s="6" t="str">
         <f aca="false">RIGHT($A2,6)</f>
         <v>Oct 21</v>
       </c>
-      <c r="D2" s="5" t="str">
-        <f aca="false">RIGHT($A2,2)</f>
+      <c r="D2" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="E2" s="6" t="str">
-        <f aca="false">TEXT(DATE(RIGHT(A2,2)+2000, MONTH(DATEVALUE(LEFT(RIGHT(A2,6),3)&amp;" 1, 2021"))+1,1),"MMM YY")</f>
-        <v>Nov 21</v>
+      <c r="E2" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="e">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6" t="e">
         <f aca="false">TEXT(DATE(RIGHT(A3,2),RIGHT(A3,6),),"MMM YY")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="5" t="str">
+      <c r="C3" s="6" t="str">
         <f aca="false">RIGHT($A3,6)</f>
         <v>Nov 21</v>
       </c>
-      <c r="D3" s="5" t="str">
-        <f aca="false">RIGHT($A3,2)</f>
+      <c r="D3" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="E3" s="6" t="str">
-        <f aca="false">TEXT(DATE(RIGHT(A3,2)+2000, MONTH(DATEVALUE(LEFT(RIGHT(A3,6),3)&amp;" 1, 2021"))+1,1),"MMM YY")</f>
-        <v>Dec 21</v>
+      <c r="E3" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5" t="str">
+      <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="6" t="str">
         <f aca="false">MID(A4,LEN(RIGHT(A4,5)),3)</f>
         <v>hly</v>
       </c>
-      <c r="C4" s="5" t="str">
+      <c r="C4" s="6" t="str">
         <f aca="false">RIGHT($A4,6)</f>
         <v>Dec 21</v>
       </c>
-      <c r="D4" s="5" t="str">
-        <f aca="false">RIGHT($A4,2)</f>
+      <c r="D4" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="E4" s="6" t="str">
-        <f aca="false">TEXT(DATE(RIGHT(A4,2)+2000, MONTH(DATEVALUE(LEFT(RIGHT(A4,6),3)&amp;" 1, 2021"))+1,1),"MMM YY")</f>
-        <v>Jan 22</v>
+      <c r="E4" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="5" t="str">
+      <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="str">
         <f aca="false">RIGHT(A5,LEN(A5)-31)</f>
         <v>n 22</v>
       </c>
-      <c r="C5" s="5" t="str">
+      <c r="C5" s="6" t="str">
         <f aca="false">RIGHT($A5,6)</f>
         <v>Jan 22</v>
       </c>
-      <c r="D5" s="5" t="str">
-        <f aca="false">RIGHT($A5,2)</f>
+      <c r="D5" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="str">
-        <f aca="false">TEXT(DATE(RIGHT(A5,2)+2000, MONTH(DATEVALUE(LEFT(RIGHT(A5,6),3)&amp;" 1, 2021"))+1,1),"MMM YY")</f>
-        <v>Feb 22</v>
+      <c r="E5" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7" t="str">
+      <c r="A6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="8" t="str">
         <f aca="false">TEXT(RIGHT(A6,6)-RIGHT(A6,3),"MMM YY")</f>
         <v>Jan 26</v>
       </c>
-      <c r="C6" s="5" t="str">
+      <c r="C6" s="6" t="str">
         <f aca="false">RIGHT($A6,6)</f>
         <v>Feb 22</v>
       </c>
-      <c r="D6" s="5" t="str">
-        <f aca="false">RIGHT($A6,2)</f>
+      <c r="D6" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="E6" s="6" t="str">
-        <f aca="false">TEXT(DATE(RIGHT(A6,2)+2000, MONTH(DATEVALUE(LEFT(RIGHT(A6,6),3)&amp;" 1, 2021"))+1,1),"MMM YY")</f>
-        <v>Mar 22</v>
+      <c r="E6" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
+      <c r="A11" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
